--- a/sample_output/공사비DB_샘플.xlsx
+++ b/sample_output/공사비DB_샘플.xlsx
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="H2" s="10">
-        <f>IFERROR(INDEX('01_시설마스터'!$V:$V,MATCH($A2,'01_시설마스터'!$A:$A,0)),"")</f>
+        <f>IFERROR(INDEX('01_시설마스터'!$V$2:$V$4,MATCH($A2,'01_시설마스터'!$A$2:$A$4,0)),"")</f>
         <v/>
       </c>
       <c r="I2" s="4" t="n">
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="H3" s="10">
-        <f>IFERROR(INDEX('01_시설마스터'!$V:$V,MATCH($A3,'01_시설마스터'!$A:$A,0)),"")</f>
+        <f>IFERROR(INDEX('01_시설마스터'!$V$2:$V$4,MATCH($A3,'01_시설마스터'!$A$2:$A$4,0)),"")</f>
         <v/>
       </c>
       <c r="I3" s="4" t="n">
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="H4" s="10">
-        <f>IFERROR(INDEX('01_시설마스터'!$V:$V,MATCH($A4,'01_시설마스터'!$A:$A,0)),"")</f>
+        <f>IFERROR(INDEX('01_시설마스터'!$V$2:$V$4,MATCH($A4,'01_시설마스터'!$A$2:$A$4,0)),"")</f>
         <v/>
       </c>
       <c r="I4" s="4" t="n">

--- a/sample_output/공사비DB_샘플.xlsx
+++ b/sample_output/공사비DB_샘플.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
